--- a/GWD Data/HP Repair Labour.xlsx
+++ b/GWD Data/HP Repair Labour.xlsx
@@ -1,12 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="HP Repair Labour" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -85,28 +89,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.00;[Red]0.00"/>
+    <numFmt numFmtId="177" formatCode="0.00;[Red]0.00"/>
   </numFmts>
   <fonts count="4">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Merriweather"/>
+      <name val="Cambria"/>
+      <family val="2"/>
     </font>
-    <font/>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Merriweather"/>
+      <name val="Cambria"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -114,27 +126,34 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB4C6E7"/>
-        <bgColor rgb="FFB4C6E7"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="15">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
@@ -143,6 +162,8 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
@@ -151,6 +172,7 @@
       </bottom>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -179,6 +201,7 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -187,6 +210,8 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -195,6 +220,7 @@
       </bottom>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -209,6 +235,7 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -254,14 +281,17 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
     </border>
     <border>
       <left style="thin">
@@ -273,8 +303,10 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -286,162 +318,319 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="2" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="2" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -582,21 +771,22 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <tabColor rgb="FFFF00FF"/>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col hidden="1" min="8" max="9" width="12.63"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F0E0350-0C7C-4FCA-AA03-E4E189E0B9A6}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -606,267 +796,234 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="12.75">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="7"/>
+    </row>
+    <row r="3" spans="1:7" ht="12.75">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="C3" s="10">
+        <v>1</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="12">
-        <v>784.0</v>
-      </c>
-      <c r="F3" s="14" t="s">
+      <c r="E3" s="10">
+        <v>784</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="15">
-        <f t="shared" ref="G3:G5" si="1">E3*C3</f>
+      <c r="G3" s="12">
+        <f>E3*C3</f>
         <v>784</v>
       </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="12.75">
+      <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="D4" s="13" t="s">
+      <c r="C4" s="10">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="13">
-        <v>714.0</v>
-      </c>
-      <c r="F4" s="14" t="s">
+      <c r="E4" s="10">
+        <v>714</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="15">
-        <f t="shared" si="1"/>
+      <c r="G4" s="12">
+        <f>E4*C4</f>
         <v>714</v>
       </c>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="s">
+    </row>
+    <row r="5" spans="1:7" ht="12.75">
+      <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="D5" s="13" t="s">
+      <c r="C5" s="10">
+        <v>4</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="13">
-        <v>645.0</v>
-      </c>
-      <c r="F5" s="14" t="s">
+      <c r="E5" s="10">
+        <v>645</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="15">
-        <f t="shared" si="1"/>
+      <c r="G5" s="12">
+        <f>E5*C5</f>
         <v>2580</v>
       </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="12.75">
+      <c r="A6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="1:7" ht="12.75">
+      <c r="A7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="D7" s="13" t="s">
+      <c r="C7" s="10">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="13">
-        <v>1400.0</v>
-      </c>
-      <c r="F7" s="14" t="s">
+      <c r="E7" s="10">
+        <v>1400</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="15">
-        <f t="shared" ref="G7:G8" si="2">E7*C7</f>
+      <c r="G7" s="12">
+        <f>E7*C7</f>
         <v>1400</v>
       </c>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="s">
+    </row>
+    <row r="8" spans="1:7" ht="12.75">
+      <c r="A8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="13">
-        <v>50.0</v>
-      </c>
-      <c r="D8" s="13" t="s">
+      <c r="C8" s="10">
+        <v>50</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="10">
         <v>2.12</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="15">
-        <f t="shared" si="2"/>
+      <c r="G8" s="12">
+        <f>E8*C8</f>
         <v>106</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="20"/>
-      <c r="B9" s="21" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="12.75">
+      <c r="A9" s="8"/>
+      <c r="B9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25">
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="18">
         <f>(SUM(G3:G5,G7:G8,))</f>
         <v>5584</v>
       </c>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="20"/>
-      <c r="B10" s="27" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="12.75">
+      <c r="A10" s="8"/>
+      <c r="B10" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="15">
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="12">
         <f>G9*1%</f>
         <v>55.84</v>
       </c>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="20"/>
-      <c r="B11" s="27" t="s">
+    </row>
+    <row r="11" spans="1:7" ht="12.75">
+      <c r="A11" s="8"/>
+      <c r="B11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="15">
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="12">
         <f>SUM(G9:G10)</f>
         <v>5639.84</v>
       </c>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="20"/>
-      <c r="B12" s="27" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="12.75">
+      <c r="A12" s="8"/>
+      <c r="B12" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="15">
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="12">
         <f>G11*15%</f>
         <v>845.976</v>
       </c>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="20"/>
-      <c r="B13" s="21" t="s">
+    </row>
+    <row r="13" spans="1:7" ht="12.75">
+      <c r="A13" s="8"/>
+      <c r="B13" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="25">
-        <f>round(SUM(G11:G12),2)</f>
+      <c r="C13" s="15"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="18">
+        <f>ROUND(SUM(G11:G12),2)</f>
         <v>6485.82</v>
       </c>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="29" t="str">
+    </row>
+    <row r="14" spans="1:7" ht="12.75">
+      <c r="A14" s="20" t="str">
         <f>CONCATENATE("Say ₹ ",G13," x Cost Index")</f>
         <v>Say ₹ 6485.82 x Cost Index</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="I14" s="32">
-        <f>G13</f>
-        <v>6485.82</v>
-      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -875,6 +1032,6 @@
     <mergeCell ref="B6:G6"/>
     <mergeCell ref="A14:G14"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/GWD Data/HP Repair Labour.xlsx
+++ b/GWD Data/HP Repair Labour.xlsx
@@ -782,7 +782,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F0E0350-0C7C-4FCA-AA03-E4E189E0B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C162532D-2F5B-4973-A3EF-8CBDF899B9A6}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/HP Repair Labour.xlsx
+++ b/GWD Data/HP Repair Labour.xlsx
@@ -782,7 +782,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C162532D-2F5B-4973-A3EF-8CBDF899B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CAD5E6D-9893-4C4F-B20E-6E45A688B9A6}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
